--- a/vlearn-app/public/quiz_excel/Day_11_Guardrails _ AI Safety/Day_11_FULL_TOAN_BO_65_CAU.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_11_Guardrails _ AI Safety/Day_11_FULL_TOAN_BO_65_CAU.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>60</v>
@@ -687,7 +687,7 @@
       <c r="J4" s="3" t="n"/>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đếm công cụ không cho biết chúng chạm vào dữ liệu hay thực hiện hành động nào.</t>
+          <t>Đếm số lượng công cụ không phản ánh đúng mức độ rủi ro; phải phân tích chi tiết dữ liệu truy cập, quyền hạn, quyền tự chủ, tính khả nghịch và hậu quả của từng công cụ.</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="G14" s="3" t="n"/>
       <c r="H14" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>60</v>
@@ -1191,7 +1191,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách hình thức của prompt khỏi mục tiêu cuối theo policy.</t>
+          <t>Bản chất của kỹ thuật jailbreak là cố tình vượt qua các chính sách và bộ lọc an toàn của hệ thống để đạt được mục tiêu bị cấm, không phụ thuộc vào việc có dùng nhập vai hay không.</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>60</v>
@@ -1237,7 +1237,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tìm mục tiêu cuối mà người dùng muốn đạt.</t>
+          <t>Một prompt sử dụng kỹ thuật nhập vai nhưng chỉ phân tích nhân vật hư cấu và không yêu cầu nội dung vi phạm chính sách thì không phải là jailbreak; cần đánh giá theo mục tiêu cuối cùng.</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>60</v>
@@ -1285,7 +1285,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đọc lịch sử như một chuỗi mục tiêu, không đặt lại ở mỗi lượt.</t>
+          <t>Khi kẻ tấn công thăm dò từng bước nhỏ (multi-turn reconnaissance), hệ thống cần phát hiện ý định tích lũy qua toàn bộ lịch sử hội thoại và chặn tại lượt 4 khi yêu cầu xâu chuỗi dữ liệu nhạy cảm xuất hiện.</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4</t>
+          <t>o2 → o3 → o4 → o1</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1385,7 +1385,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Xác định lần đầu bí mật đi khỏi ranh giới được bảo vệ.</t>
+          <t>Chuỗi rò rỉ bí mật đi từ nguồn dữ liệu lưu trữ được bảo vệ trong database (o2) → được công cụ truy xuất đưa vào context (o3) → mô hình tạo output chứa bí mật đó (o4) → gửi ra bên ngoài qua kênh HTTP sink (o1).</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="G19" s="3" t="n"/>
       <c r="H19" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I19" s="4" t="n">
         <v>60</v>
@@ -1433,7 +1433,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đếm tập thông tin đã phát hành, không chỉ phản hồi hiện tại.</t>
+          <t>Chính sách giới hạn thông tin nhạy cảm áp dụng trên toàn bộ phiên làm việc (session scope); lượt 1 và 2 đã trả 2 thuộc tính, do đó yêu cầu thuộc tính thứ 3 ở lượt 3 phải bị chặn hoặc giữ lại để không vượt quá ngưỡng tích lũy.</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="G20" s="3" t="n"/>
       <c r="H20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>60</v>
@@ -1481,7 +1481,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Khoanh vùng phiên bản, artifact và nơi chúng đã được dùng.</t>
+          <t>Khi phát hiện dependency độc hại chèn lệnh lạ ở môi trường staging, biện pháp cô lập chuẩn là phong tỏa artifact tại staging, đóng băng hoặc rollback dependency và chặn tuyệt đối đường deploy lên production.</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="G21" s="3" t="n"/>
       <c r="H21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>60</v>
@@ -1529,7 +1529,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Kiểm representation trước nội dung.</t>
+          <t>Quy tắc kiểm tra ranh giới: Lỗi encoding (byte không thể giải mã) và định dạng dữ liệu phải bị từ chối ngay tại tầng kiểm tra dữ liệu đầu vào (input validation) trước khi gửi tới mô hình.</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="G22" s="3" t="n"/>
       <c r="H22" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>60</v>
@@ -1577,7 +1577,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So quyết định trước/sau khi chuẩn hóa trên cặp biểu diễn tương đương.</t>
+          <t>Nguyên lý bất biến an toàn (safety invariance): Sau khi chuẩn hóa an toàn (loại bỏ ký tự zero-width, homoglyphs), các biểu diễn có cùng ý định ngữ nghĩa phải nhận cùng một quyết định xử lý theo chính sách.</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="G23" s="3" t="n"/>
       <c r="H23" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I23" s="4" t="n">
         <v>60</v>
@@ -1625,7 +1625,7 @@
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Rule phải nêu nó match cái gì, sau transform nào.</t>
+          <t>Khi phát hiện đầu vào khớp với chữ ký tấn công đã biết từ red-team, detector phải ghi nhận rõ quy tắc đã khớp, lý do kỹ thuật và áp dụng hành động tương ứng theo chính sách bảo mật.</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="G24" s="3" t="n"/>
       <c r="H24" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" s="4" t="n">
         <v>60</v>
@@ -1673,7 +1673,7 @@
       <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một layer cho qua không đồng nghĩa toàn bộ input an toàn.</t>
+          <t>Khi regex cho qua nhưng detector học máy (learned detector) cảnh báo tấn công với xác suất 0,91 vượt ngưỡng 0,85, hệ thống phải chặn hoặc chuyển duyệt theo kết quả learned detector, đồng thời lưu vết cả hai để kiểm toán.</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="G25" s="3" t="n"/>
       <c r="H25" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I25" s="4" t="n">
         <v>60</v>
@@ -1719,7 +1719,7 @@
       <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Không có verdict khác với verdict benign.</t>
+          <t>Kết luận 'An toàn vì ít nhất một detector đã cho qua' là sai lầm nguy hiểm; trong mô hình phòng thủ nhiều lớp, khi learned detector bị timeout thì hệ thống rơi vào trạng thái không xác định và phải xử lý fail-closed hoặc chuyển duyệt tùy mức rủi ro.</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="G26" s="3" t="n"/>
       <c r="H26" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I26" s="4" t="n">
         <v>60</v>
@@ -1767,7 +1767,7 @@
       <c r="J26" s="3" t="n"/>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Ngoài phạm vi không đồng nghĩa tấn công.</t>
+          <t>Người dùng hỏi 'quy trình nghỉ phép' nằm đúng trong phạm vi phúc lợi nhân viên; hệ thống phải đánh giá dựa trên ý định ngữ nghĩa (semantic intent) chứ không được chặn máy móc vì thiếu từ khóa 'phúc lợi'.</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1815,7 +1815,7 @@
       <c r="J27" s="3" t="n"/>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Evict timestamp cũ nhất khi nó ra khỏi 60 giây.</t>
+          <t>Cửa sổ trượt 60s cho tối đa 3 requests. Các mốc hiện tại: t=0, 20, 40s. Sự kiện tại t=0 chỉ bị loại khi t_event &lt;= now - 60 =&gt; now &gt;= 60s. Tại thời điểm hiện tại now=50s, cần thêm tối thiểu 60 - 50 = 10 giây để request cũ nhất được evict khỏi cửa sổ trượt.</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3</t>
+          <t>o2 → o3 → o1</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -1866,7 +1866,7 @@
       <c r="J28" s="3" t="n"/>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Bước cuối chỉ xuất hiện trên pass path.</t>
+          <t>Nhánh xử lý khi bị chặn: Parse/trích xuất text đầu vào của người dùng (o2) → chạy chuỗi guardrails kiểm tra theo thứ tự (o3) → trả phản hồi bị chặn và ghi log lý do kiểm toán (o1).</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="G29" s="3" t="n"/>
       <c r="H29" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I29" s="4" t="n">
         <v>60</v>
@@ -1914,7 +1914,7 @@
       <c r="J29" s="3" t="n"/>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Ai tạo dấu phân cách, và model hoặc hệ khi vận hành có thực thi vai trò đó không?</t>
+          <t>Để ngăn chặn tấn công giả mạo dấu phân cách (delimiter injection), giải pháp bền vững là sử dụng cấu trúc dữ liệu có kiểu rõ ràng (typed structured channels) kèm escaping phù hợp, coi toàn bộ tài liệu là dữ liệu thuần túy.</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="G30" s="3" t="n"/>
       <c r="H30" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I30" s="4" t="n">
         <v>60</v>
@@ -1962,7 +1962,7 @@
       <c r="J30" s="3" t="n"/>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt finding với hành động xử lý finding.</t>
+          <t>Bộ phát hiện rò rỉ dữ liệu phải nhận diện và gắn thẻ cụ thể theo từng loại và vị trí dữ liệu nhạy cảm (email, API key bí mật, mã đơn công khai) để hệ thống phía sau quyết định hành động tương ứng.</t>
         </is>
       </c>
     </row>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="G31" s="3" t="n"/>
       <c r="H31" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" s="4" t="n">
         <v>60</v>
@@ -2010,7 +2010,7 @@
       <c r="J31" s="3" t="n"/>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Policy quyết định che hay chặn dựa trên loại phát hiện và khả năng giữ phần nội dung còn hữu ích.</t>
+          <t>Khi chính sách cho phép che dữ liệu (redaction), quy trình đúng là che thông tin nhạy cảm, quét lại một lần nữa để xác nhận an toàn, rồi mới phát hành nội dung hữu ích còn lại.</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="G32" s="3" t="n"/>
       <c r="H32" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I32" s="4" t="n">
         <v>60</v>
@@ -2058,7 +2058,7 @@
       <c r="J32" s="3" t="n"/>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đừng dùng kết quả đạt của một cổng chất lượng để thay cho kết luận an toàn ở cổng khác.</t>
+          <t>Chính sách an toàn nội dung hoạt động độc lập với tính đầy đủ hay định dạng; ngay cả khi đầu ra có trích dẫn đúng và chuẩn schema, nếu chứa hướng dẫn thuộc nhóm bị cấm thì vẫn bắt buộc phải bị chặn.</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="G33" s="3" t="n"/>
       <c r="H33" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I33" s="4" t="n">
         <v>60</v>
@@ -2106,7 +2106,7 @@
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Judge phải biết đánh giá theo rule nào và phải trả theo contract nào.</t>
+          <t>Lỗ hổng thiết kế của LLM judge trong tình huống này là rubric thiếu schema định nghĩa phân loại/kết luận rõ ràng, đồng thời cấp thừa ngữ cảnh (lộ cả system prompt bí mật) cho bộ đánh giá.</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="G34" s="3" t="n"/>
       <c r="H34" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I34" s="4" t="n">
         <v>60</v>
@@ -2154,7 +2154,7 @@
       <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách collection của findings khỏi final action.</t>
+          <t>Khi có xung đột giữa các chính sách (PII yêu cầu che nhưng moderation yêu cầu chặn), hành động chặn an toàn có độ ưu tiên cao nhất, đồng thời phải lưu giữ đầy đủ các phát hiện phục vụ kiểm toán.</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="G35" s="3" t="n"/>
       <c r="H35" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I35" s="4" t="n">
         <v>60</v>
@@ -2200,7 +2200,7 @@
       <c r="J35" s="3" t="n"/>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Artifact được đánh giá trước và sau transform có cùng content hash không?</t>
+          <t>Văn bản sau khi che PII đã trở thành một artifact mới; các cổng kiểm tra an toàn và hợp đồng dữ liệu liên quan phải được chạy lại trên văn bản mới trước khi phát hành ra ngoài.</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="G37" s="3" t="n"/>
       <c r="H37" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I37" s="4" t="n">
         <v>60</v>
@@ -2296,7 +2296,7 @@
       <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một nơi hợp lệ không làm mọi dữ liệu gửi tới đó hợp lệ.</t>
+          <t>Quy tắc kiểm soát luồng dữ liệu ra ngoài (egress control): Đích đến nằm trong allowlist không đồng nghĩa được gửi mọi thứ; nếu nội dung chứa access token không cần thiết thì phải chặn không gửi.</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="G38" s="3" t="n"/>
       <c r="H38" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="4" t="n">
         <v>60</v>
@@ -2344,7 +2344,7 @@
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Lời đồng ý mơ hồ không đủ liên kết với action cụ thể.</t>
+          <t>Thao tác tài chính giá trị lớn (80 triệu) có rủi ro rất cao; khi không có mã định danh người duyệt hay chữ ký số hợp lệ trong nhật ký, hệ thống bắt buộc phải dừng thực thi (fail closed).</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I39" s="4" t="n">
@@ -2399,7 +2399,7 @@
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đừng chỉ đếm thành phần; kiểm tra xem chúng có nằm trên cùng một đường dẫn không.</t>
+          <t>Mô hình 'Lethal Trifecta' trong bảo mật agentic LLM (Simon Willison) bao gồm đúng ba thành phần trên cùng một luồng dữ liệu: (a) Tiếp nhận nội dung không đáng tin cậy từ bên ngoài (email); (b) Truy cập dữ liệu nhạy cảm nội bộ (CRM); (c) Có công cụ giao tiếp/hành động ra bên ngoài (POST ra Internet).</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="G40" s="3" t="n"/>
       <c r="H40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40" s="4" t="n">
         <v>60</v>
@@ -2447,7 +2447,7 @@
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So quyền thực tế của reader và executor, không chỉ so tên gọi.</t>
+          <t>Reader không phải là môi trường cách ly (quarantine) thực sự nếu nó vẫn giữ quyền truy cập CRM và gọi công cụ gửi email; dữ liệu lạ vẫn có thể bị lợi dụng để tấn công vào hệ thống nội bộ.</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="G41" s="3" t="n"/>
       <c r="H41" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I41" s="4" t="n">
         <v>60</v>
@@ -2495,7 +2495,7 @@
       <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Kết quả tool có quyền chọn action mới không?</t>
+          <t>Selector đã chọn cố định hành động `lookup_order`; kết quả trả về từ công cụ chỉ được xem là dữ liệu và tuyệt đối không được phép tự ý thay đổi hoặc bổ sung hành động mới (`refund_all`).</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="G43" s="3" t="n"/>
       <c r="H43" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I43" s="4" t="n">
         <v>60</v>
@@ -2594,7 +2594,7 @@
       <c r="J43" s="3" t="n"/>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Ordering dependency có thể là một safety invariant.</t>
+          <t>Thứ tự thực thi các bước (ordering dependency) thường là một bất biến an toàn; việc đổi thứ tự cấu thành thay đổi plan và bắt buộc phải qua quy trình phê duyệt lại.</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="G44" s="3" t="n"/>
       <c r="H44" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" s="4" t="n">
         <v>60</v>
@@ -2642,7 +2642,7 @@
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mỗi mapper được thấy bao nhiêu tài liệu?</t>
+          <t>Để ngăn chặn cross-document prompt injection giữa các tài liệu cạnh tranh, kiến trúc chuẩn là cô lập từng tài liệu trong một mapper riêng biệt, sau đó dùng reducer phi-LLM (deterministic) để tổng hợp kết quả có cấu trúc.</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="G45" s="3" t="n"/>
       <c r="H45" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I45" s="4" t="n">
         <v>60</v>
@@ -2690,7 +2690,7 @@
       <c r="J45" s="3" t="n"/>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dữ liệu có được phép thay đổi luồng điều khiển hoặc quyền không?</t>
+          <t>Khi xử lý tệp CSV từ bên ngoài, giải pháp an toàn là cố định logic mã nguồn từ schema đáng tin cậy và xử lý dữ liệu CSV trong môi trường sandbox được cô lập, không cho phép mô hình sinh mã động dựa trên nội dung tệp.</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="G46" s="3" t="n"/>
       <c r="H46" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I46" s="4" t="n">
         <v>60</v>
@@ -2738,7 +2738,7 @@
       <c r="J46" s="3" t="n"/>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Executor thật sự cần field nào để chạy bước đã được chốt?</t>
+          <t>Nguyên tắc đặc quyền tối thiểu (Least Privilege Context): Executor chỉ cần nhận `order_id`, action đã được chốt và các trường dữ liệu cần thiết để thực thi, không được chuyển toàn bộ lịch sử chat chứa mật khẩu và nội dung web không an toàn.</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="G50" s="3" t="n"/>
       <c r="H50" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I50" s="4" t="n">
         <v>60</v>
@@ -2930,7 +2930,7 @@
       <c r="J50" s="3" t="n"/>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Bằng chứng nào độc lập với lời agent tự khai?</t>
+          <t>Lời tự khai của agent không thể coi là bằng chứng xác thực an toàn; oracle kiểm thử bắt buộc phải quan sát các sink thực tế (canary tokens, lệnh gọi công cụ, lưu lượng mạng và thay đổi trạng thái bên ngoài).</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,5</t>
         </is>
       </c>
       <c r="I51" s="4" t="n">
@@ -2983,7 +2983,7 @@
       <c r="J51" s="3" t="n"/>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Nếu nhiều thứ cùng đổi, chênh lệch không còn gắn được cho một thay đổi cụ thể.</t>
+          <t>Để so sánh trước/sau có căn cứ khoa học (controlled comparison), phải giữ cố định các biến ngoại lai: (a) tập test case đối kháng và đối chứng lành tính, (b) quyền model/công cụ nếu chỉ đo guardrail, (c) canary và oracle chấm điểm, (e) ngưỡng điểm quyết định. Không được thay đổi ngẫu nhiên bộ prompt (d).</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="G52" s="3" t="n"/>
       <c r="H52" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I52" s="4" t="n">
         <v>60</v>
@@ -3031,7 +3031,7 @@
       <c r="J52" s="3" t="n"/>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dùng bằng chứng từ luồng điều khiển và đích nhận để quyết định.</t>
+          <t>Khi guardrail chặn yêu cầu ngay trước khi gọi mô hình, không có công cụ nào được gọi và canary không xuất hiện ở bất kỳ đích nào, kết quả kiểm thử được phân loại chính xác là 'Bị chặn' (Blocked).</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="G53" s="3" t="n"/>
       <c r="H53" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I53" s="4" t="n">
         <v>60</v>
@@ -3077,7 +3077,7 @@
       <c r="J53" s="3" t="n"/>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Oracle đã quan sát gì tại sink trước exception?</t>
+          <t>Nếu canary token đã bị rò rỉ ra sink bên ngoài trước khi tiến trình gặp exception, kết quả an toàn chính vẫn là 'Bị lộ' (Leaked); exception chỉ là sự cố thực thi phát sinh sau đó.</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -3125,7 +3125,7 @@
       <c r="J54" s="3" t="n"/>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dùng đúng mẫu số 50 tình huống được nêu trong câu.</t>
+          <t>Tỷ lệ rò rỉ (leakage rate) trên toàn bộ 50 tình huống đối kháng = (8 bị lộ / 50 tình huống) * 100% = 16%.</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -3173,7 +3173,7 @@
       <c r="J55" s="3" t="n"/>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Mẫu số là toàn bộ 80 tình huống lành tính.</t>
+          <t>Tỷ lệ chặn nhầm (False Positive Rate) trên toàn bộ 80 tình huống lành tính = (12 bị chặn nhầm / 80 tình huống) * 100% = 15%.</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="G56" s="3" t="n"/>
       <c r="H56" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I56" s="4" t="n">
         <v>60</v>
@@ -3221,7 +3221,7 @@
       <c r="J56" s="3" t="n"/>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Thành phần nào, ngoài trọng số model, còn quyết định hành vi của hệ?</t>
+          <t>Mọi thay đổi cấu hình, bao gồm cả sửa biểu thức chính quy (regex) của guardrail, đều có thể làm thay đổi ranh giới an toàn; release gate bắt buộc phải chạy lại toàn bộ bộ kiểm thử hồi quy trước khi phát hành.</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4</t>
+          <t>o2 → o3 → o1 → o4</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -3273,7 +3273,7 @@
       <c r="J57" s="3" t="n"/>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phải lưu bằng chứng trước khi sửa; chỉ thông báo sau khi kết quả đã được kiểm chứng.</t>
+          <t>Vòng đời xử lý phát hiện an toàn: Phát hiện và lưu bằng chứng đầy đủ (o2) → triển khai bản sửa lỗi trong đúng phạm vi (o3) → chạy lại test case gốc và bộ kiểm thử hồi quy regression (o1) → thông báo kết quả và rủi ro còn lại cho các bên liên quan (o4).</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="G58" s="3" t="n"/>
       <c r="H58" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I58" s="4" t="n">
         <v>60</v>
@@ -3321,7 +3321,7 @@
       <c r="J58" s="3" t="n"/>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Người duyệt phải lần từ kết luận về bằng chứng cụ thể nào?</t>
+          <t>Báo cáo an toàn có thể kiểm toán phải cung cấp chuỗi bằng chứng hoàn chỉnh: truy vết từ ca kiểm thử/nguồn đầu vào → các lớp kiểm soát tương ứng → đích gửi/verifier độc lập, kèm tỷ lệ chặn nhầm và rủi ro còn lại.</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="G59" s="3" t="n"/>
       <c r="H59" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I59" s="4" t="n">
         <v>60</v>
@@ -3369,7 +3369,7 @@
       <c r="J59" s="3" t="n"/>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Nếu sai thì hệ quả là gì và có hoàn tác được không?</t>
+          <t>Tác vụ gợi ý sắp xếp ghi chú cá nhân có hệ quả thấp và người dùng có thể hoàn tác ngay lập tức, do đó mô hình HITL phù hợp là lấy mẫu kiểm tra định kỳ và thu thập phản hồi người dùng, không cần phê duyệt bắt buộc trước.</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="G60" s="3" t="n"/>
       <c r="H60" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I60" s="4" t="n">
         <v>60</v>
@@ -3417,7 +3417,7 @@
       <c r="J60" s="3" t="n"/>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Confidence nói model chắc đến đâu; nó không quyết định hệ quả của hành động có được chấp nhận hay không.</t>
+          <t>Độ tự tin (confidence) của mô hình chỉ phản ánh sự chắc chắn về mặt toán học, không làm giảm mức độ nghiêm trọng của hậu quả; các hành động rủi ro cao bắt buộc phải có sự phê duyệt của con người theo quy định.</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="G61" s="3" t="n"/>
       <c r="H61" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I61" s="4" t="n">
         <v>60</v>
@@ -3465,7 +3465,7 @@
       <c r="J61" s="3" t="n"/>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Yếu tố nào đo mức chắc chắn, còn yếu tố nào quyết định quyền thực thi hành động hệ quả cao?</t>
+          <t>Kể cả khi mô hình đạt confidence 99,9% và đã vượt qua bộ lọc nội dung, quyền thực thi đối với các hành động rủi ro cao vẫn không được phép tự động hóa mà bắt buộc phải có sự phê duyệt của con người.</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="G62" s="3" t="n"/>
       <c r="H62" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I62" s="4" t="n">
         <v>60</v>
@@ -3513,7 +3513,7 @@
       <c r="J62" s="3" t="n"/>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Người duyệt cần biết chính xác hành động nào sẽ được thực hiện, trên đối tượng nào và với hệ quả gì.</t>
+          <t>Giao diện phê duyệt không cung cấp đối tượng, đích đến hay nội dung thay đổi sẽ dẫn đến tình trạng duyệt mù; người duyệt bắt buộc phải được cung cấp đầy đủ gói ngữ cảnh để đưa ra quyết định có căn cứ.</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4</t>
+          <t>o2 → o3 → o1 → o4</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -3565,7 +3565,7 @@
       <c r="J63" s="3" t="n"/>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Trạng thái chờ duyệt không phải đã được duyệt.</t>
+          <t>Vòng đời Human-In-The-Loop (HITL) cho hành động rủi ro cao: Tạo yêu cầu chờ duyệt có thời hạn cụ thể (o2) → người duyệt xem xét để phê duyệt/từ chối hoặc yêu cầu tự hết hạn (o3) → nếu được duyệt thì thực thi đúng hành động, nếu từ chối thì hủy (o1) → ghi nhận kết quả cuối cùng vào audit log (o4).</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="G64" s="3" t="n"/>
       <c r="H64" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I64" s="4" t="n">
         <v>60</v>
@@ -3613,7 +3613,7 @@
       <c r="J64" s="3" t="n"/>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Người điều tra sự cố ghép các bản ghi bằng khóa nào?</t>
+          <t>Việc thiếu các mã định danh tương quan chung (`request_id` / `decision_id`) khiến nhật ký kiểm toán không thể liên kết chuỗi sự kiện từ đầu vào → guardrails → phê duyệt → hành động, làm mất khả năng điều tra sự cố.</t>
         </is>
       </c>
     </row>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="G65" s="3" t="n"/>
       <c r="H65" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I65" s="4" t="n">
         <v>60</v>
@@ -3661,7 +3661,7 @@
       <c r="J65" s="3" t="n"/>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So count trên cùng lưu lượng trước khi diễn giải.</t>
+          <t>Số lần chặn tăng gấp 2 lần nhưng lưu lượng request tăng gấp 4 lần có nghĩa là tỷ lệ chặn (block rate) thực tế đã giảm một nửa; cần đánh giá theo tỷ lệ trên mẫu số lưu lượng chứ không chỉ nhìn số đếm tuyệt đối.</t>
         </is>
       </c>
     </row>
